--- a/SubClase/RUN_SubClase.xlsx
+++ b/SubClase/RUN_SubClase.xlsx
@@ -680,13 +680,13 @@
         <v>1.001347152849472</v>
       </c>
       <c r="C2" s="2">
-        <v>108.6289113343818</v>
+        <v>108.0056330309927</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E2" s="2">
-        <v>1.087752510818209</v>
+        <v>1.081511331272894</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -816,7 +816,7 @@
         <v>2.319445730201516</v>
       </c>
       <c r="C10" s="2">
-        <v>110.0976774006152</v>
+        <v>110.0976774006151</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>6</v>
@@ -949,10 +949,10 @@
         <v>22</v>
       </c>
       <c r="B18" s="2">
-        <v>0.5097302737961548</v>
+        <v>0.5097302737961549</v>
       </c>
       <c r="C18" s="2">
-        <v>107.8770429527525</v>
+        <v>107.8770429527524</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>6</v>
@@ -1230,7 +1230,7 @@
         <v>6</v>
       </c>
       <c r="E34" s="2">
-        <v>3.850638584032637</v>
+        <v>3.850638584032636</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -1425,7 +1425,7 @@
         <v>50</v>
       </c>
       <c r="B46" s="2">
-        <v>0.6352078125669371</v>
+        <v>0.635207812566937</v>
       </c>
       <c r="C46" s="2">
         <v>105.0434233047983</v>
@@ -1972,13 +1972,13 @@
         <v>15.37688065885414</v>
       </c>
       <c r="C78" s="2">
-        <v>116.9241289309075</v>
+        <v>116.9241289309076</v>
       </c>
       <c r="D78" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E78" s="2">
-        <v>17.9792837671104</v>
+        <v>17.97928376711041</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -2142,13 +2142,13 @@
         <v>1.761997110075856</v>
       </c>
       <c r="C88" s="2">
-        <v>101.5835305559906</v>
+        <v>101.5835305559907</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>6</v>
       </c>
       <c r="E88" s="2">
-        <v>1.789898872709579</v>
+        <v>1.78989887270958</v>
       </c>
     </row>
   </sheetData>
